--- a/AAII_Financials/Quarterly/BLUMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BLUMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>BLUMY</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -670,55 +670,70 @@
     <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,8 +767,20 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +814,20 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +861,20 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +888,12 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +927,20 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +974,20 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +1021,20 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1068,20 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,8 +1092,12 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1024,8 +1131,20 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1059,8 +1178,20 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1205,12 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1109,8 +1244,20 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1144,8 +1291,20 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,8 +1338,20 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1214,8 +1385,20 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1432,20 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1479,20 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1319,8 +1526,20 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1354,8 +1573,20 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1620,20 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1667,20 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1714,20 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1761,20 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1529,8 +1808,20 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1564,8 +1855,20 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1902,20 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1634,48 +1949,72 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +2028,12 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,232 +2047,308 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>361800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>361900</v>
+      </c>
+      <c r="F41" s="3">
+        <v>463100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>463300</v>
+      </c>
+      <c r="H41" s="3">
         <v>475700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>480000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>671600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>671400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>698300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>696700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>555900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>554500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>980900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>979200</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>100</v>
+      </c>
+      <c r="F42" s="3">
+        <v>14500</v>
+      </c>
+      <c r="G42" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H42" s="3">
         <v>79900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="I42" s="3">
         <v>80600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="J42" s="3">
         <v>7000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="K42" s="3">
         <v>7000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>111300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>111000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>382700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>381700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>9200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>215600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>215600</v>
+      </c>
+      <c r="F43" s="3">
+        <v>278300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>278400</v>
+      </c>
+      <c r="H43" s="3">
         <v>181300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>182900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>225900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>225800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>146100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>145800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>203800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>203300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>122900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>72100</v>
+      </c>
+      <c r="F44" s="3">
+        <v>68700</v>
+      </c>
+      <c r="G44" s="3">
+        <v>68800</v>
+      </c>
+      <c r="H44" s="3">
         <v>52100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>52500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>64300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>64300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>53900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>53800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>34400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>34400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>44700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>44700</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>15100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>15200</v>
+      </c>
+      <c r="H45" s="3">
         <v>14300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>14400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>8000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>8000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>15200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>15100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>682300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>682500</v>
+      </c>
+      <c r="F46" s="3">
+        <v>869900</v>
+      </c>
+      <c r="G46" s="3">
+        <v>870200</v>
+      </c>
+      <c r="H46" s="3">
         <v>823000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>830300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>1001000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>1000800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>1045000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>1042600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>1224500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>1221500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>1180500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>1178400</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E47" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="F47" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G47" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="H47" s="3">
         <v>1200</v>
@@ -1938,89 +2357,125 @@
         <v>1200</v>
       </c>
       <c r="J47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N47" s="3">
         <v>1300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>1300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>1900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>248500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>248500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>231500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>231500</v>
+      </c>
+      <c r="H48" s="3">
         <v>227600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>229600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>230500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>230500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>238000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>237400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>245300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>244800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>247700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>247300</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F49" s="3">
+        <v>12100</v>
+      </c>
+      <c r="G49" s="3">
+        <v>12100</v>
+      </c>
+      <c r="H49" s="3">
         <v>12900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>13000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>14100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>14100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>14300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>14300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>14700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>14700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>16200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2509,20 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2556,67 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="G52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H52" s="3">
         <v>5000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>5100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>4600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>4600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>4700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>4700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>6000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>5900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>11900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2650,67 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1044200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1044400</v>
+      </c>
+      <c r="F54" s="3">
+        <v>1200800</v>
+      </c>
+      <c r="G54" s="3">
+        <v>1201300</v>
+      </c>
+      <c r="H54" s="3">
         <v>1152800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>1163200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>1326800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>1326400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>1381400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>1378200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>1542900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>1539100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>1499700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>1497100</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2724,12 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,183 +2743,247 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>50200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>95400</v>
+      </c>
+      <c r="G57" s="3">
+        <v>95400</v>
+      </c>
+      <c r="H57" s="3">
         <v>51700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>52100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>85000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>85000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>71100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>71000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>74000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>73900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>38900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H58" s="3">
         <v>4300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>4300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>4200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>4200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>5300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>7300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>7300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>10000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>104200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>108800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>108900</v>
+      </c>
+      <c r="H59" s="3">
         <v>83200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>84000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>94200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>94200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>81000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>80800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>101500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>101200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>129800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>129600</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>160000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>208900</v>
+      </c>
+      <c r="G60" s="3">
+        <v>209000</v>
+      </c>
+      <c r="H60" s="3">
         <v>139100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>140400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>183400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>183400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>157500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>157100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>182900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>182400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>225200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F61" s="3">
+        <v>6200</v>
+      </c>
+      <c r="G61" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H61" s="3">
         <v>6600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>6700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>8600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>8600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>10500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>10500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>13000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>13000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>15200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2434,8 +3017,20 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +3064,20 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +3111,20 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +3158,67 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>184600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>184600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>235000</v>
+      </c>
+      <c r="G66" s="3">
+        <v>235100</v>
+      </c>
+      <c r="H66" s="3">
         <v>162200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>163600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>211300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>211200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>182600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>182100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>214200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>213700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>247900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>247500</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +3232,12 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +3271,20 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +3318,20 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +3365,20 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +3412,67 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>400</v>
+      </c>
+      <c r="F72" s="3">
+        <v>25100</v>
+      </c>
+      <c r="G72" s="3">
+        <v>25100</v>
+      </c>
+      <c r="H72" s="3">
         <v>11300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>11400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>67500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>67500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>106300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>106000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>233300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>232800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>169700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>169400</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +3506,20 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3553,20 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3600,67 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>859600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>859800</v>
+      </c>
+      <c r="F76" s="3">
+        <v>965800</v>
+      </c>
+      <c r="G76" s="3">
+        <v>966200</v>
+      </c>
+      <c r="H76" s="3">
         <v>990700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>999600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>1115500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>1115200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>1198800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>1196100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>1328600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>1325400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>1251800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>1249600</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3694,72 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3014,8 +3793,20 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3820,59 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H83" s="3">
         <v>6900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="I83" s="3">
         <v>6900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="J83" s="3">
         <v>6400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>7100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>6500</v>
       </c>
       <c r="K83" s="3">
         <v>6400</v>
       </c>
       <c r="L83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="M83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="N83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="O83" s="3">
+        <v>6400</v>
+      </c>
+      <c r="P83" s="3">
         <v>6100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3906,20 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3953,20 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +4000,20 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +4047,20 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +4094,67 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H89" s="3">
         <v>-18600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>-18800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>-18700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>-18700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>-38700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>-38600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>36900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>36900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>11000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +4168,59 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H91" s="3">
         <v>-4500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-4500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-4800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-5100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +4254,20 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +4301,67 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F94" s="3">
+        <v>26000</v>
+      </c>
+      <c r="G94" s="3">
+        <v>26000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-41100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-41500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>42200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>42100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>136600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>136300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-189400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-189000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-4300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,43 +4375,59 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>35400</v>
+      </c>
+      <c r="F96" s="3">
+        <v>28700</v>
+      </c>
+      <c r="G96" s="3">
+        <v>28700</v>
+      </c>
+      <c r="H96" s="3">
         <v>21200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="I96" s="3">
         <v>21400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="J96" s="3">
         <v>14200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="K96" s="3">
         <v>14200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="L96" s="3">
         <v>21100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="M96" s="3">
         <v>21000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="N96" s="3">
         <v>59900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="O96" s="3">
         <v>59800</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +4461,20 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +4508,20 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +4555,157 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="H100" s="3">
         <v>-35100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>-35500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>-37200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-37200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-26000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-25900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-64000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-63900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="J101" s="3">
         <v>2500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="K101" s="3">
         <v>2500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="L101" s="3">
         <v>-5300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="M101" s="3">
         <v>-5300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="N101" s="3">
         <v>-36700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
         <v>-36400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="P101" s="3">
         <v>8100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="Q101" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="H102" s="3">
         <v>-94400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>-95200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>-15200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>-15200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>71100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>70900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-214100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-213500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
     </row>
